--- a/光伏配储项目/电价数据/2026/坑田站.xlsx
+++ b/光伏配储项目/电价数据/2026/坑田站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.51181</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.39281</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.75822</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.5749</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.5992799999999999</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.51774</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.51628</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43767</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45452</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44553</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42386</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42318</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40909</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39872</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40154</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38492</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40261</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42321</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41261</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35466</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39152</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38501</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41699</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.3922</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.4208</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41395</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42395</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41344</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44465</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.36956</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30006</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.3155</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29501</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.31624</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.31808</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32455</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.12828</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.10437</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.11866</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.10819</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.13085</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.04906</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.10787</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.15727</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.20017</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.2784700000000001</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.09129999999999999</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.26806</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.10112</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.04476</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.15245</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21671</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.25492</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.42569</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.23929</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.17937</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.02258</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.5309400000000001</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.14306</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.39572</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.28343</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.42411</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.3871</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.21274</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.33453</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.6412</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.55983</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.5654199999999999</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.33262</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.4095299999999999</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.61649</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.46112</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.4467</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.46216</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.57787</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.47423</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.63542</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.82099</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.63975</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.6522899999999999</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.79461</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.15146</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.42923</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.68541</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.60039</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.82236</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.6649400000000001</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.6807000000000001</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.65122</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.6210599999999999</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.47736</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48129</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.39773</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41643</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42614</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32911</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.70785</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.80375</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.5532</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.86614</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53652</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5180399999999999</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50878</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48723</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40238</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46935</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38066</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37989</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39054</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33677</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37004</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36036</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37454</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.3747</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35867</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.37968</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.41833</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.49779</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.59981</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.7529</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.42831</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.38521</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.44154</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.33689</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.43213</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.5214299999999999</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.17121</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.29696</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.37162</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.06145</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.35576</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.34248</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.36872</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.35291</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.40036</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.50281</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.76728</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.16984</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.33506</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.36639</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.3806</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.38613</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.4178</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.79708</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.53906</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.34972</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.13125</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.28337</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.32052</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.38719</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.31423</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.34806</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.5139600000000001</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.34279</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.26541</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.35389</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.39482</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.1096</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.4301</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.26827</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.36325</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.43153</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.36783</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.6402</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.78579</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.62161</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.22264</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.79008</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.73942</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.66588</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.60525</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.7745</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.56796</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.45545</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.08167</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.39304</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.47042</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.6759299999999999</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44341</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43684</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.42124</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.34895</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.38065</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35824</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33469</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32144</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.51751</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.38471</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.52481</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.41781</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38201</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40425</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.41474</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38992</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38886</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36751</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43698</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.45358</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33828</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37065</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39641</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.37169</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.3723399999999999</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35612</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36163</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36709</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35929</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38517</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.3964</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47377</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.45349</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44775</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.35044</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.40069</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35302</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.37114</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.46218</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.37608</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.37863</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.36644</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.47919</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.27102</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.31988</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31828</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.32313</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.30548</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.34496</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.47606</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.40701</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.50834</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.33766</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.48629</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.42264</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.29368</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.16374</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.32461</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.27879</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.32874</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.30294</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.28251</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29319</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.34066</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.29878</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.27834</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.39811</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.40167</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.52998</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.42924</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1.19707</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.53354</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.58096</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.90022</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.39144</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.4001</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.34907</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.36752</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.5632</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.6393</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.7091499999999999</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.57714</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.33484</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.49697</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.44312</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.52644</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.42458</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.4835</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.45138</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.47304</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>1.45878</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.41681</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.38925</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.44054</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.41803</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.40532</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.41002</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36879</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34908</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34231</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31916</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.3991</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.43468</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.35153</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.36394</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.35887</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.35112</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.33325</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.32664</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.34585</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.31636</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.32165</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46069</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.32731</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.31856</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.32114</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.32977</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.32704</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.30217</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.3076</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.30364</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.29573</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.30414</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.32719</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35377</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.35399</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38929</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.3365</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.3409</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.31504</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.33966</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.34798</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.35126</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.29185</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.3534</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.37088</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.35599</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.38406</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.33634</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.33668</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.27991</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.30985</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.34828</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1.23684</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.44676</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.36666</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.09731999999999999</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.09737</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.17418</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.30464</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.28221</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.17843</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.21889</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.5106499999999999</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.06706000000000001</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.11984</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.22879</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.24282</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.37354</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.28522</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.21671</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.23647</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.20027</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.26483</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.1249</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>1.1903</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.26858</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.29805</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33644</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.30822</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33823</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.35127</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.32504</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.38997</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.44422</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.6719400000000001</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.47232</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.42732</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.36042</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.34235</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.35215</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.35496</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.32389</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.33319</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.33334</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.30168</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.3154</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32522</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.2962</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31171</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31705</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.30247</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29917</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.30377</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.41568</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38187</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35628</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33896</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.30057</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31126</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.31043</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30709</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.28912</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.3055</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.30579</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.28899</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.29319</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.28965</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.28965</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.28955</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29792</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29171</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29472</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3123</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30549</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32453</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32441</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33278</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.27835</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.25901</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.04765999999999999</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.03895000000000001</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.04858</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.04966</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04451</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.04083</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.04542</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.04245</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.0362</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04715999999999999</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.04629999999999999</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.04973</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.04761</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.04638</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04670000000000001</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.04916</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.0447</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04712</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04378</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04202</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.04487</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.04566</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.21832</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.03936</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.04524</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05511</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.0497</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.04788000000000001</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.01267</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.15532</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.05547999999999999</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.11298</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.29025</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29371</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29368</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31998</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31549</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33548</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33605</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33615</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33572</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38802</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.3924</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38782</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.3777</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34125</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.40042</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39997</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.41125</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.4673</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.3962</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.39972</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41641</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35491</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35804</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34518</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35533</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35061</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36796</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.67698</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.39945</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44469</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.422</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42186</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35967</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35846</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35795</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33188</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.3089</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32258</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.3568</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35085</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.3472</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33481</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31399</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.32942</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33439</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32139</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.2999</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32126</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33814</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.34944</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35179</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.3414</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.3156600000000001</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10255</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04371</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04543999999999999</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04563</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04675</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.09794</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>-0.00467</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04399</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04578</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04564</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04562</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04366</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04553</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04346</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04704</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.045</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04529</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04365</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.04953</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04463</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04992</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04954</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04733</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04775</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19997</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14285</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29016</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29486</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30474</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.30004</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29514</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29312</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29364</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29259</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29701</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.2909</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.2951</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26891</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29396</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29819</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30865</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30392</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30222</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31446</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31851</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34768</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34954</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34435</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36624</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36479</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33536</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33016</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31745</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31047</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40423</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34978</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32071</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.3071</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31471</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30141</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28121</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29434</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29079</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28807</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28093</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27123</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.271</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28112</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17242</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15866</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17095</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14772</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15946</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15861</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23617</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21402</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22657</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.2688</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28576</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29083</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31941</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.2908</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28093</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28111</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28052</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27171</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28102</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32246</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31025</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30502</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31639</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30956</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35915</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31653</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29832</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38389</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42873</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45707</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33205</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41889</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41576</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40279</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30013</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30101</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29945</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.30007</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15635</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29557</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31111</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31355</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31381</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32188</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34662</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30078</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38565</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50773</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.7909400000000001</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220800000000001</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40009</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49804</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78108</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92052</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49465</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.91525</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.8653200000000001</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29793</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.89036</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63221</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18993</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87015</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.53914</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33371</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03491</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53359</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7933</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.52935</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7753300000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77939</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87706</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.8750800000000001</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49533</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.40082</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.40275</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.45246</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20985</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87899</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.5511200000000001</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6246900000000001</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5390499999999999</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49854</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45621</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42464</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43769</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45011</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38893</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45277</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35206</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39996</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36516</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38574</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41457</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43351</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34373</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39017</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35048</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.3409700000000001</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33443</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34639</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40285</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34901</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45077</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35379</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40008</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.39947</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58539</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42692</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5956</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60146</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.66173</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.47363</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.41904</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.58231</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.45175</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.87803</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.628</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.87498</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.8575499999999999</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.86511</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34857</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.44298</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.32736</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33562</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30684</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.34232</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.46058</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.29427</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.29385</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31244</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35698</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33283</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.3212</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33652</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33718</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30632</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31919</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31988</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34363</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31518</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31493</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29437</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31215</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31362</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31215</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31421</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.30987</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31482</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32206</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32301</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32437</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35419</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34039</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33785</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33034</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.3371499999999999</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33512</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.4093</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.4119</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45138</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41424</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39096</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37443</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35325</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32831</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.91526</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.46341</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.40204</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.45745</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.37931</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.40918</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.35797</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.36086</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.34593</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34678</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38898</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33039</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.3588</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34536</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32273</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.39935</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.4987200000000001</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35672</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38702</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34316</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35484</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37015</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.3576</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.3627</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31629</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31355</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33247</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33799</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33743</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34915</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.3148</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31497</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29073</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.30676</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.29113</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.30056</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16656</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.31095</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30861</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.33026</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30379</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.29697</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26261</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19898</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27713</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.19046</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31036</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27818</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31132</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31196</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.35662</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35256</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.3128</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31139</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31977</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30426</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31098</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29422</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.31425</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.28922</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30744</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.31987</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.35502</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29006</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34808</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25567</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.34962</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32172</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.27571</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.33861</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27648</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.34067</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.3098</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.31811</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38524</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.33338</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43143</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.27678</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42314</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35065</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44754</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.31938</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.41976</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35872</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40098</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.39967</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.5945199999999999</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.34906</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.88975</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.32742</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.13597</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.6972200000000001</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.7871900000000001</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6426900000000001</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.57638</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.44827</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.44963</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.49959</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4392</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43635</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41441</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41233</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42252</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.49862</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41234</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43342</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41179</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43342</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.38994</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42665</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.44881</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39578</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4229</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.4327</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41234</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41238</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.39918</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42215</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39439</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.4012</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.49173</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.36189</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.34518</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.2967</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.36981</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.37444</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.31367</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.36674</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.3138</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.3626</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.95235</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.6176699999999999</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>1.23247</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>1.19604</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.25038</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>0.9945900000000001</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.69973</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.40154</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.32104</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.31187</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.67335</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.37984</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.38227</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.40366</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.41004</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.38249</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.38078</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.4416600000000001</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.3743</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.37992</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31934</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.3707</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>1.49286</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31576</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.35301</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.34078</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.40809</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.39968</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.35174</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33562</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.38752</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>1.35085</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36282</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.40501</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36235</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34902</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.5745800000000001</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46134</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.74311</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46328</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43624</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37445</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.41915</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.3851</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36817</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33319</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32837</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32327</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31836</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42085</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33802</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34266</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33753</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33465</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32414</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32741</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32412</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32293</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32188</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.30857</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32458</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31477</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.31807</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30919</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32404</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.3102</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.31584</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.31868</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.3889</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32147</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34794</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.39725</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37253</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34836</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33769</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35309</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33088</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33324</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.3184</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>1.29156</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33448</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.32056</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.33363</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>0.90454</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.3615</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.16362</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.16818</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>1.14424</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.17507</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.95301</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.94452</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.14981</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.1577</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.15001</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.15687</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.27985</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.31215</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.28799</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.30719</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.15715</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.19755</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.23088</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.23102</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.29386</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.15752</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.1627</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.31417</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.3384</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.34494</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.34053</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.35325</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>1.31881</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.35665</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.35341</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.386</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37861</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34619</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.36706</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.35955</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38354</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.4477</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.39842</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.36292</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40013</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39596</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.4393</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43771</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43706</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44194</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44309</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40151</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38958</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39677</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39064</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35849</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.35905</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34669</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34821</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33865</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.53525</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38804</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46635</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42197</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41412</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.36934</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.37947</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.37851</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37897</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.3695</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.37953</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35952</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39025</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.36956</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.37945</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.34963</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.3467</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34429</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34467</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34431</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35402</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.36951</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.37947</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35948</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33975</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.33992</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32764</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.3415</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.34819</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.35968</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29851</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31443</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31398</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30837</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29528</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.28237</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.27195</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.26677</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.20325</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30977</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.25022</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.24376</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27043</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30076</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.28844</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31788</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31539</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31021</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.34643</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31419</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29438</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.28587</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.2424</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31509</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30772</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.32298</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30666</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28602</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.31575</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.33342</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.33899</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.33411</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.33095</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.33594</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.33674</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34582</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.34043</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.33707</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.33917</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.35121</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.34684</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.31419</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.34434</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.24459</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.31703</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38074</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35623</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35758</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35484</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.37149</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.35136</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36681</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.36933</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.37937</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.37981</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38449</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34959</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.35963</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.3656</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41755</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37024</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39094</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.37996</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35196</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.3487</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35094</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.3412</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34707</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34513</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34673</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34896</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.33976</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34138</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.3425299999999999</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33771</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33965</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33006</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33122</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34331</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36183</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31008</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.3309</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33859</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32471</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32049</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33472</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32267</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.34831</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.41009</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.35626</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.31179</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.36471</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.38573</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.33551</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.4401</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.30568</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.30324</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.5098</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.16089</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.28338</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.24934</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.4494</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.1217</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.26463</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.26156</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.30937</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.32406</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.31643</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.31177</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.32223</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.32282</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.32027</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.30328</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.32295</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.36217</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.35575</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.4299</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.35349</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.35747</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.36136</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.32448</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.36574</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.32594</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.33475</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.34559</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.34369</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.34955</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.44257</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.4277</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.70068</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.37113</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.38047</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.3286</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.31761</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.32018</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.52766</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.24691</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.37883</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30648</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.3133</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32677</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.3244</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.29976</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.30524</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.29789</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.28268</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32041</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30502</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.36584</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.33258</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.32657</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.32918</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32397</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32367</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.31741</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32336</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32421</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.3234</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32662</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32765</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32637</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32675</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32379</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.32975</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32459</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.31998</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31962</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.3228</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32587</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.32945</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33407</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34513</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.33938</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.33915</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33372</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33737</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.31979</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33412</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34103</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.34566</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33447</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32905</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.32018</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32186</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32469</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31681</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.34086</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.3016</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.3443</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34425</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.31396</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.33287</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28704</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32511</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31755</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32085</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32526</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32772</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33425</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33111</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.36251</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32693</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31928</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.3195</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31525</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.35023</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>1.31567</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.32415</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.36949</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.3459100000000001</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34558</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33496</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.34976</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.34967</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.35929</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33326</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.32968</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34362</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.36722</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.3522</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.35338</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.36355</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.35832</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.37864</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38492</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37135</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.39604</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35473</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37957</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36224</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.35975</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.34876</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.3498</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34874</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34938</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33939</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35043</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34957</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35032</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.3506</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.3498</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34915</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.3494</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34624</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.3571</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34698</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34683</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34915</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33653</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33949</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.3398</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33932</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36888</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32414</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33949</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34914</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33638</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33924</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.3448</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.3356</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34918</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34918</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33622</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32793</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34818</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33985</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33613</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30723</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32777</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32908</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.3244</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31812</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31664</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31663</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.32788</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32536</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32784</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31668</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36855</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32378</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31911</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.32196</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.32257</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32367</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33152</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.33004</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32276</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.3223</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32969</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32953</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33227</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33714</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35853</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.33977</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.35413</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35358</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.3544</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36607</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.34957</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.35916</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34558</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.35847</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35857</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.3606</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34856</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.38225</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.37849</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38048</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38431</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42447</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.41122</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37936</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37631</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65623</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.76742</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.45169</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.29299</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45691</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39459</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35331</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35916</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33951</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34422</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.33711</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41095</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37599</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37044</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36169</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35888</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35856</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36172</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35799</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35868</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35255</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.3597</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.3559</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35179</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35884</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35915</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35948</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37004</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35849</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37862</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36556</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37956</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35078</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35147</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.3577</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34929</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32964</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.31878</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33419</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32652</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.28958</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.24256</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.31706</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28518</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28477</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.2007</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.26074</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.32419</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.28025</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.22024</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.27023</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28603</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.28002</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.29036</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.29374</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30653</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.33562</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.32375</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.20656</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29622</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.51193</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.35612</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32882</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.34345</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33564</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.34017</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.35957</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.50146</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.48493</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.41664</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.5158700000000001</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.49955</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.36548</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32562</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.36239</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.43652</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.3854</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.42152</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.64203</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.6075900000000001</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.59324</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.4649</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.6665099999999999</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.47008</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.82304</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.47646</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.67989</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40649</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.37326</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.35901</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.47527</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.42943</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41856</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37804</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.3745</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36678</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.35968</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34243</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.48899</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.53669</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.48484</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.49195</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41631</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39707</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40243</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.40951</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.4072</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41549</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.39803</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39447</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.40971</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.4075299999999999</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39318</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38719</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41738</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38694</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41574</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.38933</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.39889</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.39901</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41136</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.39886</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.44829</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44751</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.5570000000000001</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.49785</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.44868</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.68098</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.44985</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.46875</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.37305</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.38509</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.41658</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.44753</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.40592</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.45436</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.30219</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.37515</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.40398</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.40197</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.41626</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.33301</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.29072</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.3364</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.33206</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.34966</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.35218</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.38181</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.65144</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1.37312</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.34876</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.43077</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.29486</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.36715</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.34879</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.32961</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33427</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.35355</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.33162</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.37253</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35889</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.37285</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.35599</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.36182</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35558</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.34069</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.41781</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.43963</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.49244</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.43899</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.50864</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.51181</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.5460900000000001</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.69839</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.7300800000000001</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.48998</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.65174</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.81033</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.5907899999999999</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.52624</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.83746</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.77716</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.62749</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.67699</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.44877</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.47796</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.48341</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47617</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.46976</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41692</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.55571</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.42904</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.4411</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45556</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43521</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42473</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44536</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41661</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.39867</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.4544</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39691</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40415</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39632</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38582</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37769</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37273</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35658</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36555</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37296</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37029</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.35943</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35958</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36555</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.3856</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.3892</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37938</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36578</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36112</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35485</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.3793</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39923</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.37071</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38672</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.39942</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39415</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38615</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35116</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36892</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34419</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.3409</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.35402</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.38512</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.20748</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.39188</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.35802</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.04354</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.37199</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35088</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40334</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.35411</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.44977</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.39044</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46125</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.3288</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.31219</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.11445</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18003</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.29689</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29389</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35091</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.34854</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34775</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.35031</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.37723</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.37098</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.41686</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36964</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.43217</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.39535</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.41653</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38587</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.38074</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38491</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.39006</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40812</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.4086</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34518</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.37089</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37619</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39648</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37884</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35478</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.3988</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.3785</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.3743</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.35835</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.394</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37915</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36457</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.32852</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44366</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.36226</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.39662</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.3962</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.3777799999999999</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.34869</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37523</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.35589</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35553</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35217</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.34856</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.3559</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34486</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35104</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34771</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.33696</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.32968</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.33891</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33367</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.33865</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34363</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.32746</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.32862</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.32658</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.32639</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.3169</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.30728</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30326</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.31248</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.279</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.31776</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.31351</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.30726</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.22552</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28688</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.2306</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.28816</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25015</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.26049</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.13911</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.29456</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29817</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.31882</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.25058</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04293</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25048</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.29488</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.17118</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.18327</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.27912</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.30961</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.22986</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.25086</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.26634</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.23367</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.2762</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28414</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.28485</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.33024</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.3089</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.35214</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34725</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.3525</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.35429</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33066</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.37519</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.3606</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34434</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.31035</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35613</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35805</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.38217</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.3551</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.37031</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.36976</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.37154</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.3447</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36485</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34017</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36251</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.36679</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.35852</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34726</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34662</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34748</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.34675</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.34909</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32065</v>
+      </c>
+      <c r="C136" t="n">
+        <v>1.32572</v>
+      </c>
+      <c r="D136" t="n">
+        <v>1.33699</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34054</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34412</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33784</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.32705</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32216</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31728</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.3173</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.30567</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.30776</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31277</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.3096</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.30645</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.3073</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.30732</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.30753</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30334</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30334</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30574</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30427</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30253</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30334</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30377</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.30891</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.30753</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.28731</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.24838</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.23348</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.16084</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.19883</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.23674</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01826</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00101</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.03213000000000001</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04902</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.11028</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.02061</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03901</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04905</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01206</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.03606</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.03225</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.0471</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04647999999999999</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02409</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02149</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04909</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.20101</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04905</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04908</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04884</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.00078</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.3083</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04912</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.0489</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04907</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.03477</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04903</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04878</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.04341</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.17778</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.18956</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.23048</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.28038</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.25927</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.2567</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.26444</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.27844</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.29968</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.28657</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.28495</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.27886</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.3067</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.29361</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.3049</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.28337</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.30341</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.28281</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.29867</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.2899</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.32085</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.41059</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.32339</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.33003</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.30601</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.28742</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.28416</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.27931</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.32758</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.11517</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29803</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.55462</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.34127</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.1348</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.30149</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.27951</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.26822</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.24614</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.30176</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.2876</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.25873</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.2353</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.22316</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.25288</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.24282</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.20594</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.23101</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.23587</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.27222</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.25782</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.25642</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.23754</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.2943</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.2635</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.29811</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.34942</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.29536</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.26856</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.27035</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.21274</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.13208</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.61994</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.58913</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.63385</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.5711799999999999</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>1.14871</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>1.30619</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>1.11961</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>1.2328</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>1.1739</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.09793</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.10856</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.05793</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.22349</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.09122</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.30736</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.0029</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.01987</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.08144</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.16423</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.02883</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.09997</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.10915</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.13051</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.02612</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.08148999999999999</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.09436</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.13698</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>1.25904</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29618</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.27976</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32062</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>1.33339</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>1.33321</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>1.32875</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>1.33873</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.33388</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.33961</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.33158</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.35884</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.35927</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.37529</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.33784</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.38817</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.37791</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.45143</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.3739</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.37503</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.36234</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.3635</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>1.3547</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>1.36999</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>1.35827</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>1.36773</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.37377</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.33232</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.3272</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32816</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32901</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32912</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33798</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32277</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="C138" t="n">
+        <v>1.35445</v>
+      </c>
+      <c r="D138" t="n">
+        <v>1.37138</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.39105</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.34395</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.32947</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.32966</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.33544</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32781</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34072</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.3375</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33441</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32689</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34256</v>
+      </c>
+      <c r="R138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32269</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.31985</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.30594</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.32556</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.31637</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.31603</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.31454</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.31928</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.55432</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.5509700000000001</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.41013</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.43069</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.34651</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.32424</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.33887</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.38944</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.4504</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>1.36736</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>1.48379</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>1.39293</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.45007</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.38479</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.37844</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.36832</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.44722</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.3362</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.31455</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.33171</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.33606</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31221</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.1425</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.2790899999999999</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.27024</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30559</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.3305</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.33111</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32144</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.33494</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.2744</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.31206</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.3124</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29221</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31325</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31907</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32257</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.3278</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33265</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32602</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34899</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34643</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34802</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.34938</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34865</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35643</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33516</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.36027</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.36181</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33601</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33854</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36626</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37644</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.30111</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.5059900000000001</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.35287</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.40798</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.35743</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.38759</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.3599</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.36111</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.35509</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36968</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.34867</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.30879</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.32944</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.31934</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.32852</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.32842</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.36618</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.32995</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33001</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.27636</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31523</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.31929</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.33334</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32803</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33012</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33209</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34467</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.30271</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34825</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.33972</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33436</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.31725</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.32373</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34584</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33054</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.33946</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35361</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32249</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36825</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35431</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36872</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35877</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.36024</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.37418</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.32929</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35391</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.3772799999999999</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.6431399999999999</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.33809</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.6024</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.35067</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.50651</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.37923</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.36745</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.36374</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.31089</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.35395</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.34662</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.43452</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.36088</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.32422</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.34137</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.26346</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.34143</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35232</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32914</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.28516</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.28814</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.34088</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.34078</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.34812</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.33998</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.36624</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.36944</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.41294</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.40038</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.49367</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.50417</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.46742</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.48992</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.42439</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.58328</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.41706</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.39168</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.48916</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.35544</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.32165</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.38062</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.37158</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.35613</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.38412</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.41503</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.3707</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.37957</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.36887</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45765</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.4009</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38439</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.40462</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.38191</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37233</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36089</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36824</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34694</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.48094</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40164</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40151</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39257</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38021</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.35959</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37468</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37388</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37803</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.3764</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36837</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36654</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36104</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36006</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32714</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35579</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.35044</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34676</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.3592</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37067</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39857</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37534</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.37154</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.36191</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.36853</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.36156</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.41379</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.42014</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.38926</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.37293</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.46329</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.4032</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.38076</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.28988</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.35776</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.32947</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.37219</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.27705</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.38613</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.36777</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.36699</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29474</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.31644</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.33563</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.32038</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.32224</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.34216</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.35268</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32087</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.34588</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.36212</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.35846</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.30811</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.36101</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.35917</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.39478</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.38634</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.38979</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.37408</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.39019</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.44171</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.39717</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.42624</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.40758</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.4368</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.5143099999999999</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.5847899999999999</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.5892500000000001</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.38097</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.41036</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.5195700000000001</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.50928</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.54969</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.46654</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.37608</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.51251</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.40215</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.7299</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.89451</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.5906399999999999</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.58887</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39808</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44379</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.39889</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37456</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37689</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36739</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37286</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.25409</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36927</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.32725</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.36556</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33179</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33483</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34499</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32145</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33176</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34075</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.3364</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.35131</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33452</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.3382</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33598</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.31138</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.32004</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.31825</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.31706</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.31503</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.3178</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.31707</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.30741</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.30718</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.34816</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.36849</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.32112</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.30913</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.30343</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.29828</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.29428</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.33046</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.2939</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.31523</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.31645</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.22026</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.28717</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.31496</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.17091</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.28863</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.15429</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.07307999999999999</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.41483</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.36934</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.21293</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.04273</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.21228</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.16999</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.01125</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.31741</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.26512</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.16687</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.06331000000000001</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.06159000000000001</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.07917</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.16926</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.08487</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.0614</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.17615</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.15752</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.31357</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.2853</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.31662</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.33645</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.35471</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.38164</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.36354</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.38749</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.36128</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.37013</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.24227</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.34848</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.36318</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.30655</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.3737</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.37745</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.42505</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.37806</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.40151</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.41157</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.38504</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.39962</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.427</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.38863</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.38569</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.4201</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.37342</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.43465</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.38056</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.37247</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.35456</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.357</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.33331</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.8626</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.36687</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.46731</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.4192</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.39416</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33359</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.37715</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.38685</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.37147</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.34654</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.35383</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34039</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.36287</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.3471</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.34768</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.37017</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.38438</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.3558</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.34753</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.3574</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35163</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.35417</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35436</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.3549</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.33924</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.38596</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.34734</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.33385</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.30113</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.31834</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.30696</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.33165</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.32472</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.31411</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.29817</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.25322</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.24784</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.2707</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.24386</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.11357</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.09670000000000001</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.10347</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.14315</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.17668</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.3632</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.17532</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.00359</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.0195</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.0492</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.02085</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.02694</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.09939000000000001</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.23082</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.04909</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.23616</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>-0.01744</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.20418</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.34177</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.28561</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.32568</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32592</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.33589</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.32037</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.34604</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.33293</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.50056</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.39796</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.39243</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36213</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37304</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.39095</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36477</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34182</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.39903</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.58697</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.37386</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.3692</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.36339</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.36694</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.3713</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.35972</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.37981</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.34052</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.41348</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.39673</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.36977</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.38645</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.35722</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.35658</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.3627</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.35826</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.33366</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.62207</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.36779</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.36917</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.32195</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.35367</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.34763</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.35079</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.45685</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.33905</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.39098</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37103</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.3418</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.34648</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.32315</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33212</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.3366</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.3243</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.32686</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.34244</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.33281</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.34195</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.3361</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.33091</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.34438</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.33191</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.30802</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.27863</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.25584</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.22834</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.14288</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.20365</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.22719</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.22851</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.11317</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.14861</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>-0.00234</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04729</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.04740999999999999</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.04677000000000001</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.04758</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04740999999999999</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.04187</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.07794</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.03038</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.06274</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.09605</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.16835</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.19358</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.11929</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.25109</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.22697</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.12291</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.05562</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.26081</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.14454</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.11641</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.23502</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.18284</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.23317</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.24043</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.20121</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.24154</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.27109</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.27284</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.29706</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.30262</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.30514</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.30985</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.33052</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.33797</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.35837</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.32855</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.32339</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.34944</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.3771</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.3511</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.36135</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.36114</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.35976</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.38981</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.3949</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.46776</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.38485</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.38313</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.37849</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.38823</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.36589</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.37567</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.38128</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.3644</v>
       </c>
     </row>
   </sheetData>
